--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,6 +1188,208 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131738174</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Rödvattnet Nord, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>657776</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7075760</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131732986</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80400</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Rödvattnet Nord, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>657777</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7075761</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80400</v>
+        <v>80401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80401</v>
+        <v>80404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80404</v>
+        <v>80406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80406</v>
+        <v>80409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80409</v>
+        <v>80414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80414</v>
+        <v>80416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80381</v>
+        <v>80415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80416</v>
+        <v>80450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>131738174</v>
       </c>
       <c r="B7" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>131732986</v>
       </c>
       <c r="B8" t="n">
-        <v>80455</v>
+        <v>80457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26810-2025 artfynd.xlsx
+++ b/artfynd/A 26810-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114022589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738174</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114023489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114023490</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732986</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114023423</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,8 +1399,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114023201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>